--- a/Documentation/Specification_draft.xlsx
+++ b/Documentation/Specification_draft.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dokument\A KTH kurser\GitHub\Fundamentals-of-Flight-SD2601\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92EA06B4-04CF-41C2-84FA-1B034E1B139C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D0D50DE-92FA-4B2B-B81A-917151CF4D76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
